--- a/backtest_runs/20260410_193731/by_symbol/KTML/KTML.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/KTML/KTML.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-2394.990000000003</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>98956.03</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>98956.03</v>
@@ -771,7 +771,7 @@
         <v>-736.9199999999988</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>105445.02</v>
@@ -817,7 +817,7 @@
         <v>-1125.850000000009</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>104319.17</v>
@@ -909,7 +909,7 @@
         <v>-4257.760000000011</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>101269.14</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>101269.14</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>109968.89</v>
@@ -1185,7 +1185,7 @@
         <v>-3479.900000000006</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>107369.2</v>
@@ -1231,7 +1231,7 @@
         <v>-2845.330000000001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>104523.87</v>
@@ -1277,7 +1277,7 @@
         <v>-6345.700000000003</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>98178.16999999998</v>
@@ -1415,7 +1415,7 @@
         <v>-4380.580000000001</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>98219.10999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-2620.160000000002</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>95598.94999999998</v>
@@ -1553,7 +1553,7 @@
         <v>-962.0899999999976</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>97645.94999999998</v>
